--- a/input/mapping/060. OCB_GOLD_TCKH_V_TB_AR_DTL_3_PHAT.xlsx
+++ b/input/mapping/060. OCB_GOLD_TCKH_V_TB_AR_DTL_3_PHAT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OCB\Zone_C\Code dev lại silver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="581" documentId="13_ncr:1_{AB9DA439-EF4D-476D-A1DB-360185071422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D385BDB-D773-41E6-9588-265A28BA1EB2}"/>
+  <xr:revisionPtr revIDLastSave="589" documentId="13_ncr:1_{AB9DA439-EF4D-476D-A1DB-360185071422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F54F35B-F268-485D-9A50-210BE058338C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="3" r:id="rId1"/>
@@ -731,28 +731,9 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,     -- MAX(OU_DIM_ID) + ROW_NUMBER()
-    OU_ID           STRING,     -- branch_hashkey (SHA256)
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -760,15 +741,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực = Hub LEFT JOIN loại các khóa deleted
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
-        LEFT JOIN sts_deleted d
-            ON h.branch_hashkey = d.branch_hashkey
+        LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite (single-active): làm giàu thuộc tính, bản mới nhất đến :etl_date
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -777,7 +755,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping (single-active)
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -788,18 +765,23 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
+    area_map AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
+    ),
     source_data AS (
         SELECT
-            h.branch_hashkey                                    AS OU_ID,
-            h.business_key                                      AS OU_CODE,
-            SUBSTRING_INDEX(si.t_company_name, '::', 1)         AS OU_NM,
-            prn_hub.branch_hashkey                              AS PRN_OU_ID,
-            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)     AS PRN_OU_NM,
-            bm.parent_branch_code                               AS PRN_OU_CODE,
+            h.branch_hashkey                                AS OU_ID,
+            h.business_key                                  AS OU_CODE,
+            SUBSTRING_INDEX(si.t_company_name, '::', 1)     AS OU_NM,
+            prn_hub.branch_hashkey                          AS PRN_OU_ID,
+            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1) AS PRN_OU_NM,
+            bm.parent_branch_code                           AS PRN_OU_CODE,
             am.CB_AREA_ID,
             am.CB_AREA_NM,
-            bm.address                                          AS OU_ADR,
-            bm.phone_number                                     AS OU_PH,
+            bm.address                                      AS OU_ADR,
+            bm.phone_number                                 AS OU_PH,
             h.source_event_date
         FROM hub_active h
         LEFT JOIN sat_latest si
@@ -810,15 +792,10 @@
             ON prn_hub.business_key = bm.parent_branch_code
         LEFT JOIN sat_latest prn_si
             ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-        LEFT JOIN ou_area_mapping am
+        LEFT JOIN area_map am
             ON am.OU_ID = h.business_key
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
-    ),
-    -- Max OU_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-        FROM CB_OU_DIM
     ),
     changed AS (
         SELECT src.OU_ID
@@ -848,9 +825,8 @@
             src.source_event_date,
             src.OU_ADR,
             src.OU_PH,
-            m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID)  AS NEW_OU_DIM_ID
+            uuid()                                              AS NEW_OU_DIM_ID
         FROM source_data src
-        CROSS JOIN max_id m
         LEFT JOIN CB_OU_DIM tgt_chk
             ON  src.OU_ID        = tgt_chk.OU_ID
             AND tgt_chk.EFF_TO_DT IS NULL
@@ -859,8 +835,8 @@
     ),
     close_records AS (
         SELECT
-            'CLOSE'                                             AS rec_type,
-            'D'                                                 AS CDC_FLAG,
+            'CLOSE'                AS rec_type,
+            'D'                    AS CDC_FLAG,
             tgt.OU_ID,
             tgt.OU_NM,
             tgt.OU_CODE,
@@ -869,10 +845,10 @@
             tgt.PRN_OU_CODE,
             tgt.CB_AREA_ID,
             tgt.CB_AREA_NM,
-            tgt.START_WK_DT                                     AS source_event_date,
+            tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID                                       AS NEW_OU_DIM_ID
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -881,9 +857,25 @@
                 OR src.OU_ID IS NULL
               )
     )
-    SELECT * FROM new_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM new_records
     UNION ALL
-    SELECT * FROM close_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM close_records
 ) src
 ON  tgt.OU_ID     = src.OU_ID
 AND tgt.EFF_TO_DT IS NULL
@@ -917,8 +909,7 @@
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>V_TB_AR_DTL_3
@@ -2880,11 +2871,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3599,7 +3590,7 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="91" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3610,7 +3601,7 @@
       <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="91" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3633,7 +3624,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="83" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="93"/>
@@ -3698,7 +3689,7 @@
       <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="82" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="94"/>
@@ -4777,7 +4768,7 @@
       <c r="E88" s="14"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="83" t="s">
+      <c r="A90" s="82" t="s">
         <v>205</v>
       </c>
       <c r="B90" s="94"/>
@@ -4786,7 +4777,7 @@
       <c r="E90" s="94"/>
     </row>
     <row r="92" spans="1:5" ht="46.5" customHeight="1">
-      <c r="A92" s="82" t="s">
+      <c r="A92" s="83" t="s">
         <v>26</v>
       </c>
       <c r="B92" s="93"/>
@@ -4853,7 +4844,7 @@
       <c r="E96" s="16"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="83" t="s">
+      <c r="A97" s="82" t="s">
         <v>37</v>
       </c>
       <c r="B97" s="94"/>
@@ -5932,7 +5923,7 @@
       <c r="E179" s="14"/>
     </row>
     <row r="181" spans="1:5">
-      <c r="A181" s="83" t="s">
+      <c r="A181" s="82" t="s">
         <v>205</v>
       </c>
       <c r="B181" s="94"/>
@@ -5941,7 +5932,7 @@
       <c r="E181" s="94"/>
     </row>
     <row r="183" spans="1:5" ht="42" customHeight="1">
-      <c r="A183" s="82" t="s">
+      <c r="A183" s="83" t="s">
         <v>26</v>
       </c>
       <c r="B183" s="93"/>
@@ -6021,7 +6012,7 @@
       <c r="E188" s="16"/>
     </row>
     <row r="189" spans="1:5">
-      <c r="A189" s="83" t="s">
+      <c r="A189" s="82" t="s">
         <v>37</v>
       </c>
       <c r="B189" s="94"/>
@@ -7100,7 +7091,7 @@
       <c r="E271" s="14"/>
     </row>
     <row r="273" spans="1:5">
-      <c r="A273" s="83" t="s">
+      <c r="A273" s="82" t="s">
         <v>205</v>
       </c>
       <c r="B273" s="94"/>
@@ -7109,7 +7100,7 @@
       <c r="E273" s="94"/>
     </row>
     <row r="275" spans="1:5" ht="52.5" customHeight="1">
-      <c r="A275" s="82" t="s">
+      <c r="A275" s="83" t="s">
         <v>26</v>
       </c>
       <c r="B275" s="93"/>
@@ -7174,7 +7165,7 @@
       <c r="E279" s="16"/>
     </row>
     <row r="280" spans="1:5">
-      <c r="A280" s="83" t="s">
+      <c r="A280" s="82" t="s">
         <v>37</v>
       </c>
       <c r="B280" s="94"/>
@@ -8254,17 +8245,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A189:E189"/>
     <mergeCell ref="A273:E273"/>
     <mergeCell ref="A275:E275"/>
     <mergeCell ref="A280:E280"/>
     <mergeCell ref="A97:E97"/>
     <mergeCell ref="A181:E181"/>
     <mergeCell ref="A183:E183"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A92:E92"/>
-    <mergeCell ref="A189:E189"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9048,13 +9039,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9230,16 +9220,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27B4ACD9-F8AF-4AA9-83DF-DFD49D36ABAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCECDAC8-AA0A-48F3-AC26-1364D7A4FC25}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9247,5 +9238,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCECDAC8-AA0A-48F3-AC26-1364D7A4FC25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27B4ACD9-F8AF-4AA9-83DF-DFD49D36ABAB}"/>
 </file>